--- a/20260511_银河.xlsx
+++ b/20260511_银河.xlsx
@@ -565,13 +565,13 @@
         <v>-0.0001</v>
       </c>
       <c r="N2" s="1">
-        <v>-4.81</v>
+        <v>-5.01</v>
       </c>
       <c r="O2" s="1">
-        <v>-4.81</v>
+        <v>-5.01</v>
       </c>
       <c r="P2" s="1">
-        <v>-4.81</v>
+        <v>-5.01</v>
       </c>
       <c r="Q2" s="2">
         <v>0.0237</v>
@@ -615,13 +615,13 @@
         <v>豆粕ETF</v>
       </c>
       <c r="C3" s="1">
-        <v>864.4</v>
+        <v>865.6</v>
       </c>
       <c r="D3" s="1">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="E3" s="2">
-        <v>0.0019</v>
+        <v>0.0032</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -636,25 +636,25 @@
         <v/>
       </c>
       <c r="J3" s="1">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="K3" s="2">
-        <v>0.0017</v>
+        <v>0.0031</v>
       </c>
       <c r="L3" s="1">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="M3" s="2">
-        <v>0.0017</v>
+        <v>0.0031</v>
       </c>
       <c r="N3" s="1">
-        <v>-5.02</v>
+        <v>-4.22</v>
       </c>
       <c r="O3" s="1">
-        <v>-5.02</v>
+        <v>-4.22</v>
       </c>
       <c r="P3" s="1">
-        <v>-5.02</v>
+        <v>-4.22</v>
       </c>
       <c r="Q3" s="2">
         <v>0.0289</v>
@@ -666,10 +666,10 @@
         <v>1</v>
       </c>
       <c r="T3" s="2">
-        <v>0.0084</v>
+        <v>0.0098</v>
       </c>
       <c r="U3" s="5">
-        <v>2.161</v>
+        <v>2.164</v>
       </c>
       <c r="V3" s="5">
         <v>2.157</v>
@@ -678,16 +678,16 @@
         <v/>
       </c>
       <c r="X3" s="2">
-        <v>0.0379</v>
+        <v>0.0394</v>
       </c>
       <c r="Y3" s="2">
-        <v>0.0942</v>
+        <v>0.0957</v>
       </c>
       <c r="Z3" s="2">
-        <v>0.0936</v>
+        <v>0.0951</v>
       </c>
       <c r="AA3" s="2">
-        <v>0.129</v>
+        <v>0.1306</v>
       </c>
     </row>
     <row r="4">
@@ -781,13 +781,13 @@
         <v>300ETF</v>
       </c>
       <c r="C5" s="1">
-        <v>992</v>
+        <v>993.2</v>
       </c>
       <c r="D5" s="1">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="E5" s="2">
-        <v>0.0008</v>
+        <v>0.002</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -802,16 +802,16 @@
         <v/>
       </c>
       <c r="J5" s="1">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="K5" s="2">
-        <v>0.0007</v>
+        <v>0.0019</v>
       </c>
       <c r="L5" s="1">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="M5" s="2">
-        <v>0.0007</v>
+        <v>0.0019</v>
       </c>
       <c r="N5" s="1">
         <v>-2.42</v>
@@ -832,10 +832,10 @@
         <v>1</v>
       </c>
       <c r="T5" s="2">
-        <v>0.0151</v>
+        <v>0.0164</v>
       </c>
       <c r="U5" s="5">
-        <v>4.96</v>
+        <v>4.966</v>
       </c>
       <c r="V5" s="5">
         <v>4.957</v>
@@ -844,16 +844,16 @@
         <v/>
       </c>
       <c r="X5" s="2">
-        <v>0.0685</v>
+        <v>0.0698</v>
       </c>
       <c r="Y5" s="2">
-        <v>0.0479</v>
+        <v>0.0492</v>
       </c>
       <c r="Z5" s="2">
-        <v>0.0586</v>
+        <v>0.0599</v>
       </c>
       <c r="AA5" s="2">
-        <v>0.3191</v>
+        <v>0.3207</v>
       </c>
     </row>
     <row r="6">
@@ -864,13 +864,13 @@
         <v>黄金ETF</v>
       </c>
       <c r="C6" s="1">
-        <v>976.8</v>
+        <v>977.4</v>
       </c>
       <c r="D6" s="1">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="E6" s="2">
-        <v>0.0033</v>
+        <v>0.0039</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -885,25 +885,25 @@
         <v/>
       </c>
       <c r="J6" s="1">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="K6" s="2">
-        <v>0.0032</v>
+        <v>0.0038</v>
       </c>
       <c r="L6" s="1">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="M6" s="2">
-        <v>0.0032</v>
+        <v>0.0038</v>
       </c>
       <c r="N6" s="1">
-        <v>-3.12</v>
+        <v>-3.02</v>
       </c>
       <c r="O6" s="1">
-        <v>-3.12</v>
+        <v>-3.02</v>
       </c>
       <c r="P6" s="1">
-        <v>-3.12</v>
+        <v>-3.02</v>
       </c>
       <c r="Q6" s="2">
         <v>0.0326</v>
@@ -915,10 +915,10 @@
         <v>1</v>
       </c>
       <c r="T6" s="2">
-        <v>-0.0113</v>
+        <v>-0.0107</v>
       </c>
       <c r="U6" s="5">
-        <v>9.768</v>
+        <v>9.774</v>
       </c>
       <c r="V6" s="5">
         <v>9.737</v>
@@ -927,16 +927,16 @@
         <v/>
       </c>
       <c r="X6" s="2">
-        <v>-0.0204</v>
+        <v>-0.0198</v>
       </c>
       <c r="Y6" s="2">
-        <v>-0.0845</v>
+        <v>-0.0839</v>
       </c>
       <c r="Z6" s="2">
-        <v>0.0931</v>
+        <v>0.0937</v>
       </c>
       <c r="AA6" s="2">
-        <v>0.297</v>
+        <v>0.2978</v>
       </c>
     </row>
     <row r="7">
@@ -989,7 +989,7 @@
         <v>-5.06</v>
       </c>
       <c r="Q7" s="2">
-        <v>0.1008</v>
+        <v>0.1007</v>
       </c>
       <c r="R7" s="3">
         <v>2700</v>
@@ -1030,13 +1030,13 @@
         <v>创业板</v>
       </c>
       <c r="C8" s="1">
-        <v>787.2</v>
+        <v>789.4</v>
       </c>
       <c r="D8" s="1">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="E8" s="2">
-        <v>0.0008</v>
+        <v>0.0036</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -1051,16 +1051,16 @@
         <v/>
       </c>
       <c r="J8" s="1">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="K8" s="2">
-        <v>0.0006</v>
+        <v>0.0034</v>
       </c>
       <c r="L8" s="1">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="M8" s="2">
-        <v>0.0006</v>
+        <v>0.0034</v>
       </c>
       <c r="N8" s="1">
         <v>-4.62</v>
@@ -1081,10 +1081,10 @@
         <v>1</v>
       </c>
       <c r="T8" s="2">
-        <v>0.0342</v>
+        <v>0.037</v>
       </c>
       <c r="U8" s="5">
-        <v>3.936</v>
+        <v>3.947</v>
       </c>
       <c r="V8" s="5">
         <v>3.934</v>
@@ -1093,16 +1093,16 @@
         <v/>
       </c>
       <c r="X8" s="2">
-        <v>0.1452</v>
+        <v>0.1484</v>
       </c>
       <c r="Y8" s="2">
-        <v>0.1888</v>
+        <v>0.1921</v>
       </c>
       <c r="Z8" s="2">
-        <v>0.2464</v>
+        <v>0.2498</v>
       </c>
       <c r="AA8" s="2">
-        <v>0.9838</v>
+        <v>0.9894</v>
       </c>
     </row>
     <row r="9">
@@ -1113,13 +1113,13 @@
         <v>转债ETF</v>
       </c>
       <c r="C9" s="1">
-        <v>20326.6</v>
+        <v>20347.6</v>
       </c>
       <c r="D9" s="1">
-        <v>-49</v>
+        <v>-28</v>
       </c>
       <c r="E9" s="2">
-        <v>-0.0024</v>
+        <v>-0.0014</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -1134,16 +1134,16 @@
         <v/>
       </c>
       <c r="J9" s="1">
-        <v>-51.04</v>
+        <v>-30.04</v>
       </c>
       <c r="K9" s="2">
-        <v>-0.0025</v>
+        <v>-0.0015</v>
       </c>
       <c r="L9" s="1">
-        <v>-51.04</v>
+        <v>-30.04</v>
       </c>
       <c r="M9" s="2">
-        <v>-0.0025</v>
+        <v>-0.0015</v>
       </c>
       <c r="N9" s="1">
         <v>-30.61</v>
@@ -1155,7 +1155,7 @@
         <v>-30.61</v>
       </c>
       <c r="Q9" s="2">
-        <v>0.6788</v>
+        <v>0.6789</v>
       </c>
       <c r="R9" s="3">
         <v>1400</v>
@@ -1164,28 +1164,28 @@
         <v>1</v>
       </c>
       <c r="T9" s="2">
-        <v>0.0022</v>
+        <v>0.0032</v>
       </c>
       <c r="U9" s="5">
-        <v>14.519</v>
+        <v>14.534</v>
       </c>
       <c r="V9" s="5">
         <v>14.555</v>
       </c>
       <c r="W9" s="2">
-        <v>0.0025</v>
+        <v>0.0014</v>
       </c>
       <c r="X9" s="2">
-        <v>0.0386</v>
+        <v>0.0397</v>
       </c>
       <c r="Y9" s="2">
-        <v>-0.0047</v>
+        <v>-0.0037</v>
       </c>
       <c r="Z9" s="2">
-        <v>0.0618</v>
+        <v>0.0629</v>
       </c>
       <c r="AA9" s="2">
-        <v>0.2157</v>
+        <v>0.2169</v>
       </c>
     </row>
     <row r="10">
@@ -1196,13 +1196,13 @@
         <v>能源化工</v>
       </c>
       <c r="C10" s="1">
-        <v>665.6</v>
+        <v>665.2</v>
       </c>
       <c r="D10" s="1">
-        <v>-6.4</v>
+        <v>-6.8</v>
       </c>
       <c r="E10" s="2">
-        <v>-0.0095</v>
+        <v>-0.0101</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -1217,25 +1217,25 @@
         <v/>
       </c>
       <c r="J10" s="1">
-        <v>-6.5</v>
+        <v>-6.9</v>
       </c>
       <c r="K10" s="2">
-        <v>-0.0097</v>
+        <v>-0.0103</v>
       </c>
       <c r="L10" s="1">
-        <v>-6.5</v>
+        <v>-6.9</v>
       </c>
       <c r="M10" s="2">
-        <v>-0.0097</v>
+        <v>-0.0103</v>
       </c>
       <c r="N10" s="1">
-        <v>-5.81</v>
+        <v>-5.41</v>
       </c>
       <c r="O10" s="1">
-        <v>-5.81</v>
+        <v>-5.41</v>
       </c>
       <c r="P10" s="1">
-        <v>-5.81</v>
+        <v>-5.41</v>
       </c>
       <c r="Q10" s="2">
         <v>0.0222</v>
@@ -1247,28 +1247,28 @@
         <v>1</v>
       </c>
       <c r="T10" s="2">
-        <v>0.0171</v>
+        <v>0.0165</v>
       </c>
       <c r="U10" s="5">
-        <v>1.664</v>
+        <v>1.663</v>
       </c>
       <c r="V10" s="5">
         <v>1.68</v>
       </c>
       <c r="W10" s="2">
-        <v>0.0096</v>
+        <v>0.0102</v>
       </c>
       <c r="X10" s="2">
-        <v>0.0303</v>
+        <v>0.0297</v>
       </c>
       <c r="Y10" s="2">
-        <v>0.293</v>
+        <v>0.2922</v>
       </c>
       <c r="Z10" s="2">
-        <v>0.3517</v>
+        <v>0.3509</v>
       </c>
       <c r="AA10" s="2">
-        <v>0.303</v>
+        <v>0.3022</v>
       </c>
     </row>
     <row r="11">
@@ -1312,13 +1312,13 @@
         <v>-0.001</v>
       </c>
       <c r="N11" s="1">
-        <v>-5.02</v>
+        <v>-5.42</v>
       </c>
       <c r="O11" s="1">
-        <v>-5.02</v>
+        <v>-5.42</v>
       </c>
       <c r="P11" s="1">
-        <v>-5.02</v>
+        <v>-5.42</v>
       </c>
       <c r="Q11" s="2">
         <v>0.0287</v>
@@ -1362,13 +1362,13 @@
         <v/>
       </c>
       <c r="C12" s="1">
-        <v>29938.8</v>
+        <v>29964.6</v>
       </c>
       <c r="D12" s="1">
-        <v>-50</v>
+        <v>-24.2</v>
       </c>
       <c r="E12" s="2">
-        <v>-0.0017</v>
+        <v>-0.0008</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -1383,10 +1383,10 @@
         <v/>
       </c>
       <c r="J12" s="1">
-        <v>-52.99</v>
+        <v>-27.19</v>
       </c>
       <c r="K12" s="2">
-        <v>-0.0018</v>
+        <v>-0.0009</v>
       </c>
       <c r="L12" t="str">
         <v/>
@@ -1395,13 +1395,13 @@
         <v/>
       </c>
       <c r="N12" s="1">
-        <v>-72.6</v>
+        <v>-71.9</v>
       </c>
       <c r="O12" s="1">
-        <v>-72.6</v>
+        <v>-71.9</v>
       </c>
       <c r="P12" s="1">
-        <v>-72.6</v>
+        <v>-71.9</v>
       </c>
       <c r="Q12" s="2">
         <v>0.9997</v>

--- a/20260511_银河.xlsx
+++ b/20260511_银河.xlsx
@@ -648,13 +648,13 @@
         <v>0.0031</v>
       </c>
       <c r="N3" s="1">
-        <v>-4.22</v>
+        <v>-2.22</v>
       </c>
       <c r="O3" s="1">
-        <v>-4.22</v>
+        <v>-2.22</v>
       </c>
       <c r="P3" s="1">
-        <v>-4.22</v>
+        <v>-2.22</v>
       </c>
       <c r="Q3" s="2">
         <v>0.0289</v>
@@ -731,13 +731,13 @@
         <v>-0.0001</v>
       </c>
       <c r="N4" s="1">
-        <v>-6.11</v>
+        <v>-5.01</v>
       </c>
       <c r="O4" s="1">
-        <v>-6.11</v>
+        <v>-5.01</v>
       </c>
       <c r="P4" s="1">
-        <v>-6.11</v>
+        <v>-5.01</v>
       </c>
       <c r="Q4" s="2">
         <v>0.0246</v>
@@ -814,13 +814,13 @@
         <v>0.0019</v>
       </c>
       <c r="N5" s="1">
-        <v>-2.42</v>
+        <v>-3.02</v>
       </c>
       <c r="O5" s="1">
-        <v>-2.42</v>
+        <v>-3.02</v>
       </c>
       <c r="P5" s="1">
-        <v>-2.42</v>
+        <v>-3.02</v>
       </c>
       <c r="Q5" s="2">
         <v>0.0331</v>
@@ -897,13 +897,13 @@
         <v>0.0038</v>
       </c>
       <c r="N6" s="1">
-        <v>-3.02</v>
+        <v>-1.22</v>
       </c>
       <c r="O6" s="1">
-        <v>-3.02</v>
+        <v>-1.22</v>
       </c>
       <c r="P6" s="1">
-        <v>-3.02</v>
+        <v>-1.22</v>
       </c>
       <c r="Q6" s="2">
         <v>0.0326</v>
@@ -1063,13 +1063,13 @@
         <v>0.0034</v>
       </c>
       <c r="N8" s="1">
-        <v>-4.62</v>
+        <v>-2.22</v>
       </c>
       <c r="O8" s="1">
-        <v>-4.62</v>
+        <v>-2.22</v>
       </c>
       <c r="P8" s="1">
-        <v>-4.62</v>
+        <v>-2.22</v>
       </c>
       <c r="Q8" s="2">
         <v>0.0263</v>
@@ -1146,13 +1146,13 @@
         <v>-0.0015</v>
       </c>
       <c r="N9" s="1">
-        <v>-30.61</v>
+        <v>-33.41</v>
       </c>
       <c r="O9" s="1">
-        <v>-30.61</v>
+        <v>-33.41</v>
       </c>
       <c r="P9" s="1">
-        <v>-30.61</v>
+        <v>-33.41</v>
       </c>
       <c r="Q9" s="2">
         <v>0.6789</v>
@@ -1229,13 +1229,13 @@
         <v>-0.0103</v>
       </c>
       <c r="N10" s="1">
-        <v>-5.41</v>
+        <v>-11.81</v>
       </c>
       <c r="O10" s="1">
-        <v>-5.41</v>
+        <v>-11.81</v>
       </c>
       <c r="P10" s="1">
-        <v>-5.41</v>
+        <v>-11.81</v>
       </c>
       <c r="Q10" s="2">
         <v>0.0222</v>
@@ -1312,13 +1312,13 @@
         <v>-0.001</v>
       </c>
       <c r="N11" s="1">
-        <v>-5.42</v>
+        <v>-5.82</v>
       </c>
       <c r="O11" s="1">
-        <v>-5.42</v>
+        <v>-5.82</v>
       </c>
       <c r="P11" s="1">
-        <v>-5.42</v>
+        <v>-5.82</v>
       </c>
       <c r="Q11" s="2">
         <v>0.0287</v>
@@ -1395,13 +1395,13 @@
         <v/>
       </c>
       <c r="N12" s="1">
-        <v>-71.9</v>
+        <v>-74.8</v>
       </c>
       <c r="O12" s="1">
-        <v>-71.9</v>
+        <v>-74.8</v>
       </c>
       <c r="P12" s="1">
-        <v>-71.9</v>
+        <v>-74.8</v>
       </c>
       <c r="Q12" s="2">
         <v>0.9997</v>

--- a/20260511_银河.xlsx
+++ b/20260511_银河.xlsx
@@ -1499,7 +1499,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1538,34 +1538,28 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-06</v>
       </c>
       <c r="B2" t="str">
-        <v>14:02:01</v>
+        <v/>
       </c>
       <c r="C2" t="str">
-        <v>510300</v>
+        <v/>
       </c>
       <c r="D2" t="str">
-        <v>300ETF</v>
+        <v/>
       </c>
       <c r="E2" t="str">
-        <v>买入</v>
+        <v>银行转证券</v>
       </c>
       <c r="F2">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>4.956</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>-991.2</v>
-      </c>
-      <c r="I2" s="6">
-        <v>991.2</v>
-      </c>
-      <c r="J2" s="6">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="K2" t="str">
         <v/>
@@ -1576,13 +1570,13 @@
         <v>2026-05-11</v>
       </c>
       <c r="B3" t="str">
-        <v>14:02:37</v>
+        <v>14:02:01</v>
       </c>
       <c r="C3" t="str">
-        <v>512100</v>
+        <v>510300</v>
       </c>
       <c r="D3" t="str">
-        <v>1000ETF</v>
+        <v>300ETF</v>
       </c>
       <c r="E3" t="str">
         <v>买入</v>
@@ -1591,13 +1585,13 @@
         <v>200</v>
       </c>
       <c r="G3">
-        <v>3.555</v>
+        <v>4.956</v>
       </c>
       <c r="H3">
-        <v>-711</v>
+        <v>-991.2</v>
       </c>
       <c r="I3" s="6">
-        <v>711</v>
+        <v>991.2</v>
       </c>
       <c r="J3" s="6">
         <v>0</v>
@@ -1611,13 +1605,13 @@
         <v>2026-05-11</v>
       </c>
       <c r="B4" t="str">
-        <v>14:02:50</v>
+        <v>14:02:37</v>
       </c>
       <c r="C4" t="str">
-        <v>159915</v>
+        <v>512100</v>
       </c>
       <c r="D4" t="str">
-        <v>创业板</v>
+        <v>1000ETF</v>
       </c>
       <c r="E4" t="str">
         <v>买入</v>
@@ -1626,13 +1620,13 @@
         <v>200</v>
       </c>
       <c r="G4">
-        <v>3.933</v>
+        <v>3.555</v>
       </c>
       <c r="H4">
-        <v>-786.6</v>
+        <v>-711</v>
       </c>
       <c r="I4" s="6">
-        <v>786.6</v>
+        <v>711</v>
       </c>
       <c r="J4" s="6">
         <v>0</v>
@@ -1646,28 +1640,28 @@
         <v>2026-05-11</v>
       </c>
       <c r="B5" t="str">
-        <v>14:03:06</v>
+        <v>14:02:50</v>
       </c>
       <c r="C5" t="str">
-        <v>513010</v>
+        <v>159915</v>
       </c>
       <c r="D5" t="str">
-        <v>港股科技</v>
+        <v>创业板</v>
       </c>
       <c r="E5" t="str">
         <v>买入</v>
       </c>
       <c r="F5">
-        <v>1100</v>
+        <v>200</v>
       </c>
       <c r="G5">
-        <v>0.67</v>
+        <v>3.933</v>
       </c>
       <c r="H5">
-        <v>-737</v>
+        <v>-786.6</v>
       </c>
       <c r="I5" s="6">
-        <v>737</v>
+        <v>786.6</v>
       </c>
       <c r="J5" s="6">
         <v>0</v>
@@ -1681,28 +1675,28 @@
         <v>2026-05-11</v>
       </c>
       <c r="B6" t="str">
-        <v>14:03:51</v>
+        <v>14:03:06</v>
       </c>
       <c r="C6" t="str">
-        <v>518880</v>
+        <v>513010</v>
       </c>
       <c r="D6" t="str">
-        <v>黄金ETF</v>
+        <v>港股科技</v>
       </c>
       <c r="E6" t="str">
         <v>买入</v>
       </c>
       <c r="F6">
-        <v>100</v>
+        <v>1100</v>
       </c>
       <c r="G6">
-        <v>9.736</v>
+        <v>0.67</v>
       </c>
       <c r="H6">
-        <v>-973.6</v>
+        <v>-737</v>
       </c>
       <c r="I6" s="6">
-        <v>973.6</v>
+        <v>737</v>
       </c>
       <c r="J6" s="6">
         <v>0</v>
@@ -1716,28 +1710,28 @@
         <v>2026-05-11</v>
       </c>
       <c r="B7" t="str">
-        <v>14:04:05</v>
+        <v>14:03:51</v>
       </c>
       <c r="C7" t="str">
-        <v>159981</v>
+        <v>518880</v>
       </c>
       <c r="D7" t="str">
-        <v>能源化工</v>
+        <v>黄金ETF</v>
       </c>
       <c r="E7" t="str">
         <v>买入</v>
       </c>
       <c r="F7">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="G7">
-        <v>1.68</v>
+        <v>9.736</v>
       </c>
       <c r="H7">
-        <v>-672</v>
+        <v>-973.6</v>
       </c>
       <c r="I7" s="6">
-        <v>672</v>
+        <v>973.6</v>
       </c>
       <c r="J7" s="6">
         <v>0</v>
@@ -1751,13 +1745,13 @@
         <v>2026-05-11</v>
       </c>
       <c r="B8" t="str">
-        <v>14:04:16</v>
+        <v>14:04:05</v>
       </c>
       <c r="C8" t="str">
-        <v>159985</v>
+        <v>159981</v>
       </c>
       <c r="D8" t="str">
-        <v>豆粕ETF</v>
+        <v>能源化工</v>
       </c>
       <c r="E8" t="str">
         <v>买入</v>
@@ -1766,13 +1760,13 @@
         <v>400</v>
       </c>
       <c r="G8">
-        <v>2.157</v>
+        <v>1.68</v>
       </c>
       <c r="H8">
-        <v>-862.8</v>
+        <v>-672</v>
       </c>
       <c r="I8" s="6">
-        <v>862.8</v>
+        <v>672</v>
       </c>
       <c r="J8" s="6">
         <v>0</v>
@@ -1786,28 +1780,28 @@
         <v>2026-05-11</v>
       </c>
       <c r="B9" t="str">
-        <v>14:04:34</v>
+        <v>14:04:16</v>
       </c>
       <c r="C9" t="str">
-        <v>511380</v>
+        <v>159985</v>
       </c>
       <c r="D9" t="str">
-        <v>转债ETF</v>
+        <v>豆粕ETF</v>
       </c>
       <c r="E9" t="str">
         <v>买入</v>
       </c>
       <c r="F9">
-        <v>1400</v>
+        <v>400</v>
       </c>
       <c r="G9">
-        <v>14.554</v>
+        <v>2.157</v>
       </c>
       <c r="H9">
-        <v>-20375.6</v>
+        <v>-862.8</v>
       </c>
       <c r="I9" s="6">
-        <v>20375.6</v>
+        <v>862.8</v>
       </c>
       <c r="J9" s="6">
         <v>0</v>
@@ -1821,28 +1815,28 @@
         <v>2026-05-11</v>
       </c>
       <c r="B10" t="str">
-        <v>14:04:49</v>
+        <v>14:04:34</v>
       </c>
       <c r="C10" t="str">
-        <v>166016</v>
+        <v>511380</v>
       </c>
       <c r="D10" t="str">
-        <v>中欧纯债</v>
+        <v>转债ETF</v>
       </c>
       <c r="E10" t="str">
         <v>买入</v>
       </c>
       <c r="F10">
-        <v>2700</v>
+        <v>1400</v>
       </c>
       <c r="G10">
-        <v>1.118</v>
+        <v>14.554</v>
       </c>
       <c r="H10">
-        <v>-3018.6</v>
+        <v>-20375.6</v>
       </c>
       <c r="I10" s="6">
-        <v>3018.6</v>
+        <v>20375.6</v>
       </c>
       <c r="J10" s="6">
         <v>0</v>
@@ -1856,40 +1850,75 @@
         <v>2026-05-11</v>
       </c>
       <c r="B11" t="str">
-        <v>14:05:33</v>
+        <v>14:04:49</v>
       </c>
       <c r="C11" t="str">
-        <v>159980</v>
+        <v>166016</v>
       </c>
       <c r="D11" t="str">
-        <v>有色ETF</v>
+        <v>中欧纯债</v>
       </c>
       <c r="E11" t="str">
         <v>买入</v>
       </c>
       <c r="F11">
-        <v>400</v>
+        <v>2700</v>
       </c>
       <c r="G11">
-        <v>2.151</v>
+        <v>1.118</v>
       </c>
       <c r="H11">
-        <v>-860.4</v>
+        <v>-3018.6</v>
       </c>
       <c r="I11" s="6">
-        <v>860.4</v>
+        <v>3018.6</v>
       </c>
       <c r="J11" s="6">
         <v>0</v>
       </c>
       <c r="K11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>2026-05-11</v>
+      </c>
+      <c r="B12" t="str">
+        <v>14:05:33</v>
+      </c>
+      <c r="C12" t="str">
+        <v>159980</v>
+      </c>
+      <c r="D12" t="str">
+        <v>有色ETF</v>
+      </c>
+      <c r="E12" t="str">
+        <v>买入</v>
+      </c>
+      <c r="F12">
+        <v>400</v>
+      </c>
+      <c r="G12">
+        <v>2.151</v>
+      </c>
+      <c r="H12">
+        <v>-860.4</v>
+      </c>
+      <c r="I12" s="6">
+        <v>860.4</v>
+      </c>
+      <c r="J12" s="6">
+        <v>0</v>
+      </c>
+      <c r="K12" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K12"/>
   </ignoredErrors>
 </worksheet>
 </file>